--- a/Lambda_Document_Processor_Performance_Analysis.xlsx
+++ b/Lambda_Document_Processor_Performance_Analysis.xlsx
@@ -1150,8 +1150,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -1180,8 +1180,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
@@ -1493,7 +1493,9 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1594,7 +1596,17 @@
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" customWidth="1"/>
+    <col min="11" max="11" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1818,7 +1830,11 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="46.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2222,7 +2238,10 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2389,7 +2408,13 @@
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="2" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" customWidth="1"/>
+    <col min="6" max="7" width="20.7109375" customWidth="1"/>
+    <col min="8" max="8" width="31.7109375" customWidth="1"/>
+    <col min="9" max="9" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2547,7 +2572,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="29.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2680,7 +2710,8 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2814,7 +2845,11 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2947,7 +2982,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">

--- a/Lambda_Document_Processor_Performance_Analysis.xlsx
+++ b/Lambda_Document_Processor_Performance_Analysis.xlsx
@@ -12,17 +12,18 @@
     <sheet name="Function Breakdown" sheetId="3" r:id="rId3"/>
     <sheet name="Performance Summary" sheetId="4" r:id="rId4"/>
     <sheet name="Cost Analysis" sheetId="5" r:id="rId5"/>
-    <sheet name="Optimization Options" sheetId="6" r:id="rId6"/>
-    <sheet name="Technical Specifications" sheetId="7" r:id="rId7"/>
-    <sheet name="Competitive Analysis" sheetId="8" r:id="rId8"/>
-    <sheet name="Risk Assessment" sheetId="9" r:id="rId9"/>
+    <sheet name="Pricing Breakdown" sheetId="6" r:id="rId6"/>
+    <sheet name="Optimization Options" sheetId="7" r:id="rId7"/>
+    <sheet name="Technical Specifications" sheetId="8" r:id="rId8"/>
+    <sheet name="Competitive Analysis" sheetId="9" r:id="rId9"/>
+    <sheet name="Risk Assessment" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="286">
   <si>
     <t>Metric</t>
   </si>
@@ -384,6 +385,9 @@
     <t>Cost per Document ($)</t>
   </si>
   <si>
+    <t>Cost Formula</t>
+  </si>
+  <si>
     <t>Monthly Cost ($)</t>
   </si>
   <si>
@@ -408,9 +412,84 @@
     <t>Enterprise Scale</t>
   </si>
   <si>
+    <t>(32.5s × 3GB × $0.0000166667) + (2 batches × $0.0000002)</t>
+  </si>
+  <si>
+    <t>(145.0s × 3GB × $0.0000166667) + (25 batches × $0.0000002)</t>
+  </si>
+  <si>
+    <t>(770.0s × 3GB × $0.0000166667) + (150 batches × $0.0000002)</t>
+  </si>
+  <si>
+    <t>(2520.0s × 3GB × $0.0000166667) + (500 batches × $0.0000002)</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Basis</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
     <t>Impact</t>
   </si>
   <si>
+    <t>Lambda Compute</t>
+  </si>
+  <si>
+    <t>Lambda Requests</t>
+  </si>
+  <si>
+    <t>Memory Allocation</t>
+  </si>
+  <si>
+    <t>Processing Time</t>
+  </si>
+  <si>
+    <t>Batch Size</t>
+  </si>
+  <si>
+    <t>$0.0000166667 per GB-second</t>
+  </si>
+  <si>
+    <t>$0.0000002 per request</t>
+  </si>
+  <si>
+    <t>AWS Lambda pricing for 3GB memory allocation</t>
+  </si>
+  <si>
+    <t>AWS Lambda pricing for invocations</t>
+  </si>
+  <si>
+    <t>Required for PaddleOCR models in memory</t>
+  </si>
+  <si>
+    <t>Measured performance: 0.5s per page + one-time cold start</t>
+  </si>
+  <si>
+    <t>Current architecture design for optimal performance</t>
+  </si>
+  <si>
+    <t>Model loading time measured in testing</t>
+  </si>
+  <si>
+    <t>3GB (3008MB)</t>
+  </si>
+  <si>
+    <t>10 pages per Lambda</t>
+  </si>
+  <si>
+    <t>Pages × 0.5s + 20s cold start</t>
+  </si>
+  <si>
+    <t>20s per container</t>
+  </si>
+  <si>
     <t>Cost</t>
   </si>
   <si>
@@ -423,6 +502,12 @@
     <t>Implementation</t>
   </si>
   <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>Timeline Reason</t>
+  </si>
+  <si>
     <t>Increase Batch Size to 50 pages</t>
   </si>
   <si>
@@ -465,6 +550,21 @@
     <t>Same per page</t>
   </si>
   <si>
+    <t>5-20 instances × $0.0000097 per GB-second × 3GB × 2,592,000s/month</t>
+  </si>
+  <si>
+    <t>Same total processing time, fewer Lambda invocations</t>
+  </si>
+  <si>
+    <t>Saves 0.15s per page × $0.00005 per second</t>
+  </si>
+  <si>
+    <t>Saves 0.2s per page × $0.00005 per second</t>
+  </si>
+  <si>
+    <t>Same total compute, distributed across multiple Lambdas</t>
+  </si>
+  <si>
     <t>20s per job</t>
   </si>
   <si>
@@ -507,7 +607,34 @@
     <t>Architecture change</t>
   </si>
   <si>
-    <t>Component</t>
+    <t>1 day</t>
+  </si>
+  <si>
+    <t>2-3 days</t>
+  </si>
+  <si>
+    <t>1 week</t>
+  </si>
+  <si>
+    <t>1-2 weeks</t>
+  </si>
+  <si>
+    <t>2-4 weeks</t>
+  </si>
+  <si>
+    <t>Simple AWS console configuration change</t>
+  </si>
+  <si>
+    <t>Code modification + testing + deployment</t>
+  </si>
+  <si>
+    <t>Feature flag implementation + A/B testing</t>
+  </si>
+  <si>
+    <t>Model testing + accuracy validation + deployment</t>
+  </si>
+  <si>
+    <t>Architecture redesign + SQS/SNS setup + testing + deployment</t>
   </si>
   <si>
     <t>Specification</t>
@@ -681,7 +808,7 @@
     <t>Mitigation</t>
   </si>
   <si>
-    <t>Timeline</t>
+    <t>Cost Basis</t>
   </si>
   <si>
     <t>Cold Start Latency</t>
@@ -720,7 +847,19 @@
     <t>Savings</t>
   </si>
   <si>
-    <t>1 day</t>
+    <t>10 instances × $0.0000097/GB-s × 3GB × 2,592,000s</t>
+  </si>
+  <si>
+    <t>Configuration change only</t>
+  </si>
+  <si>
+    <t>CloudWatch monitoring + additional compute for A/B testing</t>
+  </si>
+  <si>
+    <t>AWS support request, no additional charges</t>
+  </si>
+  <si>
+    <t>Automated S3 lifecycle transitions reduce storage costs</t>
   </si>
   <si>
     <t>Immediate</t>
@@ -729,14 +868,26 @@
     <t>2 weeks</t>
   </si>
   <si>
-    <t>1 week</t>
+    <t>AWS console configuration, no code changes required</t>
+  </si>
+  <si>
+    <t>Simple parameter adjustment in existing code</t>
+  </si>
+  <si>
+    <t>Setup monitoring infrastructure + implement A/B framework</t>
+  </si>
+  <si>
+    <t>AWS support ticket processing time + approval</t>
+  </si>
+  <si>
+    <t>S3 lifecycle policy configuration + testing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,6 +899,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -794,13 +953,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1591,6 +1753,182 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="29.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="50.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="50.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
@@ -2405,19 +2743,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="33.7109375" customWidth="1"/>
     <col min="2" max="3" width="19.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" customWidth="1"/>
-    <col min="6" max="7" width="20.7109375" customWidth="1"/>
-    <col min="8" max="8" width="31.7109375" customWidth="1"/>
-    <col min="9" max="9" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="50.7109375" customWidth="1"/>
+    <col min="7" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="31.7109375" customWidth="1"/>
+    <col min="10" max="10" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>115</v>
       </c>
@@ -2445,10 +2784,13 @@
       <c r="I1" s="1" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B2" s="2">
         <v>25</v>
@@ -2462,22 +2804,25 @@
       <c r="E2" s="2">
         <v>0.00162540325</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G2" s="2">
         <v>1.62540325</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>19.504839</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>0.5416666666666666</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2">
         <v>9.027777777777779</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="2">
         <v>250</v>
@@ -2491,22 +2836,25 @@
       <c r="E3" s="2">
         <v>0.0072550145</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="2">
         <v>3.62750725</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>43.530087</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <v>2.416666666666667</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="2">
         <v>20.13888888888889</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" s="2">
         <v>1500</v>
@@ -2520,22 +2868,25 @@
       <c r="E4" s="2">
         <v>0.038530077</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="2">
         <v>3.8530077</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>46.2360924</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>12.83333333333333</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>21.38888888888889</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B5" s="2">
         <v>5000</v>
@@ -2549,16 +2900,19 @@
       <c r="E5" s="2">
         <v>0.126100252</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="2">
         <v>6.3050126</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>75.6601512</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>42</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>35</v>
       </c>
     </row>
@@ -2569,135 +2923,93 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="33.7109375" customWidth="1"/>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="5" width="29.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>132</v>
+      <c r="A1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" t="s">
         <v>152</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="2" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" t="s">
         <v>154</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2706,6 +3018,201 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="33.7109375" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="50.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
+    <col min="9" max="9" width="50.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2716,68 +3223,68 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>162</v>
+        <v>204</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>173</v>
+        <v>215</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>174</v>
+        <v>216</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2785,21 +3292,21 @@
         <v>76</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>177</v>
+        <v>219</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>187</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>169</v>
+        <v>211</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>188</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2807,32 +3314,32 @@
         <v>73</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>170</v>
+        <v>212</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>181</v>
+        <v>223</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>191</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2840,7 +3347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2854,39 +3361,39 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>235</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="B2" s="2">
         <v>120</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>245</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>113</v>
@@ -2894,19 +3401,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>199</v>
+        <v>241</v>
       </c>
       <c r="B3" s="2">
         <v>60</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>204</v>
+        <v>246</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>114</v>
@@ -2914,19 +3421,19 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>200</v>
+        <v>242</v>
       </c>
       <c r="B4" s="2">
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>205</v>
+        <v>247</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>114</v>
@@ -2934,19 +3441,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="B5" s="2">
         <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>206</v>
+        <v>248</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>114</v>
@@ -2954,160 +3461,22 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="B6" s="2">
         <v>30</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>207</v>
+        <v>249</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>111</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="29.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/Lambda_Document_Processor_Performance_Analysis.xlsx
+++ b/Lambda_Document_Processor_Performance_Analysis.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="286">
   <si>
     <t>Metric</t>
   </si>
@@ -887,7 +887,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -899,14 +899,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -953,16 +945,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2925,90 +2914,170 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>145</v>
       </c>
+      <c r="D2" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="E2" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F2" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>146</v>
       </c>
+      <c r="D3" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="E3" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F3" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>151</v>
       </c>
+      <c r="E4" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F4" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="F5" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="E6" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F6" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F7" t="s">
+      <c r="D7" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="E7" s="2" t="e">
+        <f>#NUM!</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>154</v>
       </c>
     </row>
